--- a/CIVE-202_Spring-2026_Group-152_02_Project_4_Timesheet.xlsx
+++ b/CIVE-202_Spring-2026_Group-152_02_Project_4_Timesheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/67405100@nebraska.edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carterjanssen/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{152C64C3-A618-D04D-BE7B-833831106124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D94AC00-BAB2-5C4B-A345-5F48C020E51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{9195B219-0828-614F-8AA7-F4A1058364B9}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16840" xr2:uid="{9195B219-0828-614F-8AA7-F4A1058364B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -128,7 +128,16 @@
     <t>4hr</t>
   </si>
   <si>
-    <t>10 min</t>
+    <t>1hr</t>
+  </si>
+  <si>
+    <t>Houry Rate</t>
+  </si>
+  <si>
+    <t>16.5 total</t>
+  </si>
+  <si>
+    <t>$412.5 total</t>
   </si>
 </sst>
 </file>
@@ -526,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9A94C9-F2BD-804E-B36F-F8B1E9754C97}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
@@ -536,7 +545,7 @@
     <col min="5" max="5" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,8 +561,11 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>46133</v>
       </c>
@@ -569,8 +581,11 @@
       <c r="E2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>46115</v>
       </c>
@@ -586,8 +601,11 @@
       <c r="E3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>46133</v>
       </c>
@@ -603,8 +621,11 @@
       <c r="E4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>46133</v>
       </c>
@@ -620,8 +641,11 @@
       <c r="E5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>46132</v>
       </c>
@@ -637,8 +661,11 @@
       <c r="E6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>46133</v>
       </c>
@@ -654,8 +681,11 @@
       <c r="E7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>46133</v>
       </c>
@@ -666,13 +696,16 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>46133</v>
       </c>
@@ -687,6 +720,17 @@
       </c>
       <c r="E9" t="s">
         <v>14</v>
+      </c>
+      <c r="F9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
